--- a/landing_zone/2026/Honda/2025-06/2026_Honda_Accessories-06-2025.xlsx
+++ b/landing_zone/2026/Honda/2025-06/2026_Honda_Accessories-06-2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pbssystems-my.sharepoint.com/personal/paxm_pbssystems_com/Documents/Desktop/Office/Projects/OEM Accessory project/OEM Accessories_v1/landing_zone/2026/Honda/2025-06/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="818" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{986A5247-C35B-426E-96E0-CEB87B4C737E}"/>
+  <xr:revisionPtr revIDLastSave="819" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{236AACBE-6BC5-4787-8466-09E34BBD6A29}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Upload - HRV " sheetId="22" r:id="rId1"/>
@@ -3140,7 +3140,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
